--- a/resources/templates/Template Laporan RTM Program Studi.xlsx
+++ b/resources/templates/Template Laporan RTM Program Studi.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sinyo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SiGKM\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCF3BEA-6956-4C24-AAE1-1858E4C89950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B221CAF-3C58-4DF7-8DED-58FFF1EF955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{25A54871-B160-4DEC-8B58-332D550846FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Laporan RTM Program Studi" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="diploma" localSheetId="0">#REF!</definedName>
     <definedName name="diploma">#REF!</definedName>
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>KEMENTERIAN PENDIDIKAN TINGGI, SAINS, DAN TEKNOLOGI</t>
   </si>
@@ -119,13 +116,34 @@
   </si>
   <si>
     <t>Kupang, ……..................................2026</t>
+  </si>
+  <si>
+    <t>Mengetahui</t>
+  </si>
+  <si>
+    <t>Koordinator Prodi</t>
+  </si>
+  <si>
+    <t>Ketua GKM</t>
+  </si>
+  <si>
+    <t>Anggota GKM</t>
+  </si>
+  <si>
+    <t>(Dr. YULIANTO TRIWAHYUADI POLLY, S.Kom., M.Cs)</t>
+  </si>
+  <si>
+    <t>(CLARISSA ELFIRA AMOS PAH, M.T.I)</t>
+  </si>
+  <si>
+    <t>(NELCI DESSY RUMLAKLAK, S.KOM, M.KOM)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +206,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -378,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -386,48 +418,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -443,67 +478,68 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -622,454 +658,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3932767</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>176953</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1397000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>143086</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C955BA-24EF-4195-938C-0BB7CC56C5B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19706167" y="4380653"/>
-          <a:ext cx="1394883" cy="1255183"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Ketua GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1336887</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>922866</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>113454</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA65A044-43F7-40F6-AA89-B40EB375B157}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22939587" y="4381501"/>
-          <a:ext cx="1167129" cy="1224703"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Anggota GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1394459</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1236133</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEAA2B4A-B2FA-40F8-8687-374633D6320E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15472409" y="4410710"/>
-          <a:ext cx="3753274" cy="1257300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Mengetahui</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Koord. Prodi</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="TM Standar Mutu Prog.Studi"/>
-      <sheetName val="TM IKU-IKK Prog.Studi"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1362,329 +951,329 @@
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.08984375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="53.81640625" style="5" customWidth="1"/>
-    <col min="5" max="6" width="55.81640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="24.36328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="31.6328125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="24.54296875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="27.1796875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="22.6328125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="20.36328125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="26.1796875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="28.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.90625" style="5"/>
+    <col min="1" max="1" width="5.54296875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="53.81640625" style="3" customWidth="1"/>
+    <col min="5" max="6" width="55.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.36328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="31.6328125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.54296875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="27.1796875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.36328125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="26.1796875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="28.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="4"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="33"/>
     </row>
     <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
-      <c r="D2" s="7" t="s">
+      <c r="A2" s="4"/>
+      <c r="D2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="8"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="35"/>
     </row>
     <row r="3" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="D3" s="9" t="s">
+      <c r="A3" s="4"/>
+      <c r="D3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="10"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="37"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="4"/>
+      <c r="D4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="12"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="39"/>
     </row>
     <row r="5" spans="1:16" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="D5" s="13" t="s">
+      <c r="A5" s="4"/>
+      <c r="D5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="14"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="41"/>
     </row>
     <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
-      <c r="D6" s="13" t="s">
+      <c r="A6" s="4"/>
+      <c r="D6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="14"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="41"/>
     </row>
     <row r="7" spans="1:16" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="18"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="19"/>
     </row>
     <row r="8" spans="1:16" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
     </row>
     <row r="9" spans="1:16" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
     </row>
     <row r="10" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="21" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="11" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="21" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="31" t="s">
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="31" t="s">
+      <c r="L11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="31" t="s">
+      <c r="M11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="P11" s="31" t="s">
+      <c r="P11" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="35" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="38">
+      <c r="A13" s="10">
         <v>1</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="10">
         <v>2</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="10">
         <v>3</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="11">
         <v>4</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="11">
         <v>5</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="11">
         <v>6</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="10">
         <v>7</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="10">
         <v>8</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="12">
         <v>9</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="13">
         <v>10</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="13">
         <v>11</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="13">
         <v>12</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="13">
         <v>13</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="13">
         <v>14</v>
       </c>
-      <c r="O13" s="41">
+      <c r="O13" s="13">
         <v>15</v>
       </c>
-      <c r="P13" s="41">
+      <c r="P13" s="13">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="7:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:13" x14ac:dyDescent="0.35">
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
@@ -1695,7 +1284,7 @@
       </c>
       <c r="M17"/>
     </row>
-    <row r="18" spans="7:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:13" x14ac:dyDescent="0.35">
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
@@ -1704,87 +1293,100 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G19"/>
-      <c r="H19"/>
+    <row r="19" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F19" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="43"/>
       <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
+    <row r="20" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F20" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44" t="s">
+        <v>29</v>
+      </c>
       <c r="M20"/>
     </row>
-    <row r="21" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
+    <row r="21" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
+    <row r="22" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
+    <row r="23" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
+    <row r="24" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
+    <row r="25" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
       <c r="M25"/>
     </row>
-    <row r="26" spans="7:13" x14ac:dyDescent="0.35">
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
+    <row r="26" spans="6:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44" t="s">
+        <v>32</v>
+      </c>
       <c r="M26"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="D6:P6"/>
+    <mergeCell ref="D1:P1"/>
+    <mergeCell ref="D2:P2"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="D4:P4"/>
+    <mergeCell ref="D5:P5"/>
     <mergeCell ref="D7:P7"/>
     <mergeCell ref="B8:P8"/>
     <mergeCell ref="B9:P9"/>
@@ -1795,12 +1397,13 @@
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="G10:P10"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D1:P1"/>
-    <mergeCell ref="D2:P2"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="D4:P4"/>
-    <mergeCell ref="D5:P5"/>
-    <mergeCell ref="D6:P6"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O11:O12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="122" scale="72" orientation="landscape" r:id="rId1"/>
